--- a/output/pdf_financials_xlsx/SERV.xlsx
+++ b/output/pdf_financials_xlsx/SERV.xlsx
@@ -3944,7 +3944,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">

--- a/output/pdf_financials_xlsx/SERV.xlsx
+++ b/output/pdf_financials_xlsx/SERV.xlsx
@@ -802,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.183055</v>
+        <v>0.209376</v>
       </c>
     </row>
     <row r="29">
@@ -815,7 +815,7 @@
         <v>-1.126654</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.025955</v>
+        <v>-1.999634</v>
       </c>
     </row>
     <row r="30">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-34.82529039195995</v>
+        <v>-34.37284378361635</v>
       </c>
     </row>
     <row r="31">
@@ -1736,7 +1736,7 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.209376</v>
       </c>
     </row>
     <row r="101">
@@ -1998,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>9.313069</v>
       </c>
     </row>
     <row r="121">
@@ -3172,7 +3172,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -3226,7 +3230,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3460,7 +3464,11 @@
           <t>Issuance of common shares, net of issuance costs 17</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SERV.xlsx
+++ b/output/pdf_financials_xlsx/SERV.xlsx
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.14122</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>1.390867</v>
       </c>
     </row>
     <row r="68">
